--- a/output/pdf_financials_xlsx/SLX.P.xlsx
+++ b/output/pdf_financials_xlsx/SLX.P.xlsx
@@ -760,16 +760,16 @@
         <v>-0.033018</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.073958</v>
+        <v>-0.073958</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0.058615</v>
+        <v>-0.058615</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>0.092337</v>
+        <v>-0.092337</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.024716</v>
+        <v>-0.024716</v>
       </c>
     </row>
     <row r="17">
@@ -868,16 +868,16 @@
         <v>-0.033018</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.073958</v>
+        <v>-0.073958</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0.058615</v>
+        <v>-0.058615</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>0.092337</v>
+        <v>-0.092337</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0.024716</v>
+        <v>-0.024716</v>
       </c>
     </row>
     <row r="21">
@@ -934,16 +934,16 @@
         <v>-0.033018</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.073958</v>
+        <v>-0.073958</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>0.058615</v>
+        <v>-0.058615</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>0.092337</v>
+        <v>-0.092337</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>0.024716</v>
+        <v>-0.024716</v>
       </c>
     </row>
     <row r="24">
@@ -1000,13 +1000,13 @@
         <v>0.471686</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>-1.232633</v>
+        <v>1.232633</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>-2.93075</v>
+        <v>2.93075</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>-3.0779</v>
+        <v>3.0779</v>
       </c>
       <c r="F26" s="1" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>-0.033018</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.073958</v>
+        <v>-0.073958</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0.058615</v>
+        <v>-0.058615</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>0.092337</v>
+        <v>-0.092337</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0.024716</v>
+        <v>-0.024716</v>
       </c>
     </row>
     <row r="28">
@@ -1068,16 +1068,16 @@
         <v>-0.033018</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.073958</v>
+        <v>-0.073958</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.058615</v>
+        <v>-0.058615</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>0.092337</v>
+        <v>-0.092337</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.024716</v>
+        <v>-0.024716</v>
       </c>
     </row>
     <row r="30">
@@ -1122,16 +1122,16 @@
         <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -5225,16 +5225,16 @@
         </is>
       </c>
       <c r="F43" s="5" t="n">
-        <v>0.073958</v>
+        <v>-0.073958</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.058615</v>
+        <v>-0.058615</v>
       </c>
       <c r="H43" s="5" t="n">
-        <v>0.092337</v>
+        <v>-0.092337</v>
       </c>
       <c r="I43" s="5" t="n">
-        <v>0.024716</v>
+        <v>-0.024716</v>
       </c>
     </row>
     <row r="44">
@@ -6317,10 +6317,10 @@
         </is>
       </c>
       <c r="E70" s="5" t="n">
-        <v>0.033018</v>
+        <v>-0.033018</v>
       </c>
       <c r="F70" s="5" t="n">
-        <v>0.073958</v>
+        <v>-0.073958</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/SLX.P.xlsx
+++ b/output/pdf_financials_xlsx/SLX.P.xlsx
@@ -1180,19 +1180,19 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.069193</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.203039</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.117072</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.030413</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.004125</v>
       </c>
     </row>
     <row r="35">
@@ -1224,19 +1224,19 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.069193</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.203039</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.117072</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.030413</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.004125</v>
       </c>
     </row>
     <row r="37">
@@ -3565,7 +3565,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
